--- a/accountant-skill/data/Jan2026/books_of_prime_entry_Jan2026.xlsx
+++ b/accountant-skill/data/Jan2026/books_of_prime_entry_Jan2026.xlsx
@@ -1,21 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sales" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Purchases" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Receipts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cash Payments" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Payroll" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="General" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="PC Summary" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="CC Summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchases" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Receipts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Payments" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,12 +80,6 @@
       <color rgb="00FF0000"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FF0000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -133,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -163,19 +155,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -543,11 +522,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -791,30 +770,30 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>1020</v>
+        <v>1320</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Cash at Bank — Main Account</t>
+          <t>Account 1320</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>5440000</v>
+        <v>0</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>5501500</v>
+        <v>20000</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>-61500</v>
+        <v>-20000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>1030</v>
+        <v>10000</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Petty Cash</t>
+          <t>Cash in hand</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
@@ -829,49 +808,49 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>1100</v>
+        <v>10100</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>4525000</v>
+        <v>5440000</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1965000</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>2560000</v>
+        <v>5501500</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>-61500</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>1110</v>
+        <v>11000</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Allowance for Doubtful Debts</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>15000</v>
+        <v>4540000</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0</v>
+        <v>1965000</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>15000</v>
+        <v>2575000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>1200</v>
+        <v>12000</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Inventory — Raw Materials</t>
+          <t>Inventory - Raw Material</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
@@ -886,68 +865,68 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>1320</v>
+        <v>20000</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Prepaid Insurance</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>0</v>
+        <v>798000</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>20000</v>
+        <v>1916000</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>-20000</v>
+        <v>-1118000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>2010</v>
+        <v>22200</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>798000</v>
+        <v>0</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>1916000</v>
+        <v>205000</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>-1118000</v>
+        <v>-205000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>2030</v>
+        <v>30200</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Accrued Wages &amp; Salaries</t>
+          <t>Account 30200</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>205000</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>-205000</v>
+        <v>0</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>200000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>3010</v>
+        <v>31000</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Owner's Capital</t>
+          <t>Paid-up Capital</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
@@ -962,382 +941,192 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>3020</v>
+        <v>40000</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Owner's Drawings</t>
+          <t>Sales Revenue</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>200000</v>
+        <v>7515000</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>-7515000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>4010</v>
+        <v>50000</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 1</t>
+          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>0</v>
+        <v>2096000</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>1710000</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>-1710000</v>
+        <v>0</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>2096000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>4020</v>
+        <v>50100</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 2</t>
+          <t xml:space="preserve">Opening Inventory - Packaging </t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2090000</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>-2090000</v>
+        <v>0</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>225000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>4030</v>
+        <v>60000</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 3</t>
+          <t>Marketing &amp; Advertising Expense</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>1310000</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>-1310000</v>
+        <v>0</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>120000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>4040</v>
+        <v>61000</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Sales Revenue — General</t>
+          <t>Office Salaries</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>0</v>
+        <v>2755000</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>2405000</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>-2405000</v>
+        <v>0</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>2755000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>5010</v>
+        <v>62000</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Raw Materials Used</t>
+          <t>Meal Allowance Expense</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>2096000</v>
+        <v>120000</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>2096000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>5020</v>
+        <v>63000</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Packaging Costs</t>
+          <t>Utilities (Electricity &amp; Water)</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>225000</v>
+        <v>125000</v>
       </c>
       <c r="D33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>225000</v>
+        <v>125000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>5100</v>
+        <v>64000</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Salaries &amp; Wages</t>
+          <t>Transportation &amp; Distribution Expense</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>2755000</v>
+        <v>85000</v>
       </c>
       <c r="D34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>2755000</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>5110</v>
+        <v>65000</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Employee Benefits</t>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>120000</v>
+        <v>1480500</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>120000</v>
+        <v>1480500</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>5200</v>
+        <v>68000</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Rent Expense</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>1180000</v>
+        <v>0</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="6" t="n">
-        <v>1180000</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n">
-        <v>5210</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Utilities Expense</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>125000</v>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="6" t="n">
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="n">
-        <v>5220</v>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Telephone &amp; Internet</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>55000</v>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="6" t="n">
-        <v>55000</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="n">
-        <v>5400</v>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Repairs &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>95000</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="6" t="n">
-        <v>95000</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="n">
-        <v>5410</v>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Office Supplies</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="n">
         <v>12000</v>
       </c>
-      <c r="D40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="n">
-        <v>5420</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Cleaning &amp; Sanitation</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>45000</v>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="6" t="n">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="n">
-        <v>5500</v>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Delivery</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="n">
-        <v>85000</v>
-      </c>
-      <c r="D42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="6" t="n">
-        <v>85000</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="n">
-        <v>5600</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Marketing &amp; Advertising</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>120000</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="6" t="n">
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="n">
-        <v>5700</v>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Insurance Expense</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="n">
-        <v>85000</v>
-      </c>
-      <c r="D44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="6" t="n">
-        <v>85000</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="n">
-        <v>5900</v>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Miscellaneous Expense</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E45" s="10" t="n">
+      <c r="E36" s="10" t="n">
         <v>-12000</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="n">
-        <v>5920</v>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Bank Charges &amp; Fees</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="n">
-        <v>8500</v>
-      </c>
-      <c r="D46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="6" t="n">
-        <v>8500</v>
       </c>
     </row>
   </sheetData>
@@ -1358,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1415,7 +1204,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>4525000</v>
@@ -1432,7 +1221,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>4010</v>
+        <v>40000</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>0</v>
@@ -1441,91 +1230,40 @@
         <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1015000</v>
+        <v>4525000</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>4020</v>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>1390000</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>4030</v>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>890000</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>4040</v>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>1230000</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B8" s="8" t="n">
         <v>4525000</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C8" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D8" s="8" t="n">
         <v>4525000</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E8" s="8" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Balance Check:</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1604,7 +1342,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>0</v>
@@ -1621,7 +1359,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>1646000</v>
@@ -1638,7 +1376,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>5020</v>
+        <v>50100</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>225000</v>
@@ -1655,7 +1393,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>5420</v>
+        <v>65000</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>45000</v>
@@ -1719,7 +1457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1776,7 +1514,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>5440000</v>
@@ -1793,7 +1531,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>0</v>
@@ -1810,7 +1548,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>3010</v>
+        <v>31000</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>0</v>
@@ -1827,7 +1565,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>4010</v>
+        <v>40000</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>0</v>
@@ -1836,91 +1574,40 @@
         <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>695000</v>
+        <v>2990000</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>4020</v>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>700000</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>4030</v>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>420000</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>4040</v>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>1175000</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B10" s="8" t="n">
         <v>5440000</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C10" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D10" s="8" t="n">
         <v>5440000</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E10" s="8" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Balance Check:</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1942,7 +1629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1999,41 +1686,41 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>1020</v>
+        <v>10000</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2823000</v>
+        <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>1030</v>
+        <v>10100</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0</v>
+        <v>2823000</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>798000</v>
@@ -2050,7 +1737,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>3020</v>
+        <v>30200</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>200000</v>
@@ -2067,13 +1754,13 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>5200</v>
+        <v>60000</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>1180000</v>
+        <v>120000</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>0</v>
@@ -2084,7 +1771,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>5210</v>
+        <v>63000</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>125000</v>
@@ -2101,10 +1788,10 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>5220</v>
+        <v>64000</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>55000</v>
+        <v>85000</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>1</v>
@@ -2118,13 +1805,13 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>5400</v>
+        <v>65000</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>95000</v>
+        <v>1395000</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>0</v>
@@ -2133,85 +1820,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>5500</v>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>85000</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>5600</v>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>120000</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>5700</v>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>65000</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B14" s="8" t="n">
         <v>2823000</v>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C14" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D14" s="8" t="n">
         <v>2823000</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E14" s="8" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Balance Check:</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2290,7 +1926,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>0</v>
@@ -2307,7 +1943,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>2030</v>
+        <v>22200</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>0</v>
@@ -2324,7 +1960,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>5100</v>
+        <v>61000</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>2755000</v>
@@ -2341,7 +1977,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>5110</v>
+        <v>62000</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>120000</v>
@@ -2405,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2462,7 +2098,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>1020</v>
+        <v>1320</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>0</v>
@@ -2471,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>8500</v>
+        <v>20000</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1</v>
@@ -2479,7 +2115,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>1100</v>
+        <v>10100</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>0</v>
@@ -2488,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>15000</v>
+        <v>8500</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1</v>
@@ -2496,7 +2132,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>1110</v>
+        <v>11000</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>15000</v>
@@ -2505,15 +2141,15 @@
         <v>1</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>1200</v>
+        <v>12000</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>0</v>
@@ -2530,30 +2166,30 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>1320</v>
+        <v>50000</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>5010</v>
+        <v>65000</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>450000</v>
+        <v>40500</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>0</v>
@@ -2564,685 +2200,52 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>5410</v>
+        <v>68000</v>
       </c>
       <c r="B11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>12000</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="E11" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>5700</v>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>5900</v>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>5920</v>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>8500</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>TOTALS</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>505500</v>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>505500</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Balance Check:</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0070AD47"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Profit Center Summary — P&amp;L View</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01 to 2026-01-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Soft Drink</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Drinking Water</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Shared / Corporate</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Sales Revenue</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>1710000</v>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>2405000</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>7515000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>TOTAL REVENUE</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="n">
-        <v>1710000</v>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>2405000</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>7515000</v>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>COST OF GOODS SOLD</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cost of Goods Sold</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="n">
-        <v>-1518000</v>
-      </c>
-      <c r="C10" s="15" t="n">
-        <v>-745000</v>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>-58000</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-2321000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>TOTAL COGS</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>-1518000</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>-745000</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>-58000</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>-2321000</v>
       </c>
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>GROSS PROFIT</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>192000</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>2655000</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>2347000</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>5194000</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>GM%: 69.1%</t>
-        </is>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>505500</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>505500</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>OPERATING EXPENSES</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="n">
-        <v>-835000</v>
-      </c>
-      <c r="C16" s="15" t="n">
-        <v>-960000</v>
-      </c>
-      <c r="D16" s="15" t="n">
-        <v>-2882000</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>-4677000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>TOTAL OPEX</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>-835000</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>-960000</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>-2882000</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>-4677000</v>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>OPERATING PROFIT</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n">
-        <v>-643000</v>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>1695000</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>-535000</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>517000</v>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>NON-OPERATING EXPENSES</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Non-Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D22" s="15" t="n">
-        <v>-8500</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>-8500</v>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>NET PROFIT / (LOSS)</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>-643000</v>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>1695000</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>-543500</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>508500</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A9:E9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0070AD47"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Cost Center Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-01 to 2026-01-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>CC Code</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Cost Center Name</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Total Costs (Dr)</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Total Credits</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Net Cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>CC101</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Soft Drink Production</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>2060000</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>2060000</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>CC102</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Drinking Water Production</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>1145000</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>1145000</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>CC103</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Water Treatment</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>488000</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>488000</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>CC104</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Preform Production</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>198000</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>198000</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>CC105</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Filling &amp; Packaging</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>225000</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>225000</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>CC201</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Factory Utilities</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>955000</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>955000</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>CC202</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>140000</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>140000</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>CC301</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Sales &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>565000</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>565000</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>CC302</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Administration</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>1230500</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>1230500</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n">
-        <v>7006500</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>7006500</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Balance Check:</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/accountant-skill/data/Jan2026/books_of_prime_entry_Jan2026.xlsx
+++ b/accountant-skill/data/Jan2026/books_of_prime_entry_Jan2026.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>505500</v>
+        <v>1220500</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>505500</v>
+        <v>1220500</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>18084500</v>
+        <v>18799500</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>18084500</v>
+        <v>18799500</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
@@ -865,267 +865,514 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>20000</v>
+        <v>12400</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Work-in-Progress</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>798000</v>
+        <v>65000</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1916000</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>-1118000</v>
+        <v>50000</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>22200</v>
+        <v>20000</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Wages Payable</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>0</v>
+        <v>798000</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>205000</v>
+        <v>1916000</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>-205000</v>
+        <v>-1118000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>30200</v>
+        <v>22200</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Account 30200</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>200000</v>
+        <v>205000</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>-205000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>31000</v>
+        <v>30200</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Paid-up Capital</t>
+          <t>Account 30200</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>500000</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>-500000</v>
+        <v>0</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>200000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>40000</v>
+        <v>31000</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Sales Revenue</t>
+          <t>Paid-up Capital</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>7515000</v>
+        <v>500000</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>-7515000</v>
+        <v>-500000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
+          <t>Sales Revenue</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>2096000</v>
+        <v>0</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>2096000</v>
+        <v>7515000</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>-7515000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>50100</v>
+        <v>50000</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opening Inventory - Packaging </t>
+          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>225000</v>
+        <v>2096000</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>225000</v>
+        <v>2096000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>60000</v>
+        <v>50010</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Advertising Expense</t>
+          <t>Purchases Raw Materials</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="6" t="n">
         <v>120000</v>
       </c>
-      <c r="D30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>120000</v>
+      <c r="E30" s="10" t="n">
+        <v>-120000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>61000</v>
+        <v>50100</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Office Salaries</t>
+          <t xml:space="preserve">Opening Inventory - Packaging </t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>2755000</v>
+        <v>225000</v>
       </c>
       <c r="D31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>2755000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>62000</v>
+        <v>50110</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Meal Allowance Expense</t>
+          <t>Purchases Packaging</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>120000</v>
+        <v>30000</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>-30000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>63000</v>
+        <v>50300</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Utilities (Electricity &amp; Water)</t>
+          <t>Opening Work-in-Progress</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>125000</v>
+        <v>50000</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>64000</v>
+        <v>50310</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Transportation &amp; Distribution Expense</t>
+          <t>Closing Work-in-Progress</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>85000</v>
+        <v>65000</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>-65000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>65000</v>
+        <v>50320</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+          <t>Direct Materials Used</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>1480500</v>
+        <v>150000</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>1480500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
+        <v>50330</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Direct Labor Transferred to WIP</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>50340</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturing Overhead Applied</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>50350</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>WIP Transferred to Finished Goods</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>325000</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>325000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>53000</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Direct Labor Wages</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>-80000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>53100</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Machine Maintenance &amp; Repair Expense</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>-15000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>53200</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Production Utilities (Electricity &amp; Water)</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>-20000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>53300</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Depreciation Expenses - COGS</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-10000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Advertising Expense</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>61000</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Office Salaries</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>2755000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>62000</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Meal Allowance Expense</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>63000</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Utilities (Electricity &amp; Water)</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>125000</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>64000</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Distribution Expense</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>85000</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>65000</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>1480500</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>1480500</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
         <v>68000</v>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>Other Expenses</t>
         </is>
       </c>
-      <c r="C36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="6" t="n">
+      <c r="C49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="6" t="n">
         <v>12000</v>
       </c>
-      <c r="E36" s="10" t="n">
+      <c r="E49" s="10" t="n">
         <v>-12000</v>
       </c>
     </row>
@@ -2041,7 +2288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2166,30 +2413,30 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
+        <v>12400</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="E9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>65000</v>
+        <v>50000</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>40500</v>
+        <v>450000</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>0</v>
@@ -2200,49 +2447,270 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
+        <v>50010</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>50110</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>50300</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>50310</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>50320</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>50330</v>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>50340</v>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>50350</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>325000</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>53000</v>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>53100</v>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>53200</v>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>53300</v>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>65000</v>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>40500</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
         <v>68000</v>
       </c>
-      <c r="B11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="6" t="n">
+      <c r="B24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="6" t="n">
         <v>12000</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="E24" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
-        <v>505500</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>505500</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="B26" s="8" t="n">
+        <v>1220500</v>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>1220500</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Balance Check:</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/accountant-skill/data/Jan2026/books_of_prime_entry_Jan2026.xlsx
+++ b/accountant-skill/data/Jan2026/books_of_prime_entry_Jan2026.xlsx
@@ -14,6 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Payments" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PC Summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CC Summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +83,12 @@
       <color rgb="00FF0000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -125,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -155,6 +164,19 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1387,6 +1409,76 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Exceptions &amp; Flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Journal</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Row 7</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Debit account 50300 (expense) requires a Cost Center</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2723,4 +2815,586 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Profit Center Summary — P&amp;L View</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01 to 2026-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Soft Drink</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Drinking Water</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Shared / Corporate</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sales Revenue</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>2405000</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>7515000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>1710000</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>2405000</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>7515000</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>COST OF GOODS SOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cost of Goods Sold</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>-2073000</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>-745000</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>-153000</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>-2971000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL COGS</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>-2073000</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>-745000</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>-153000</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-2971000</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>GROSS PROFIT</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>-363000</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>2655000</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>2252000</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>4544000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>GM%: 60.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>-835000</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>-960000</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>-2890500</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>-4685500</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL OPEX</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="n">
+        <v>-835000</v>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>-960000</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>-2890500</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>-4685500</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>OPERATING PROFIT</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n">
+        <v>-1198000</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>1695000</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>-638500</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>-141500</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>NON-OPERATING EXPENSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Non-Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>NET PROFIT / (LOSS)</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>-1198000</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>1695000</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>-638500</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>-141500</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A9:E9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cost Center Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01 to 2026-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CC Code</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Cost Center Name</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Total Costs (Dr)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Total Credits</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Net Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>CC101</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Soft Drink Production</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2260000</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2260000</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>CC102</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Drinking Water Production</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1145000</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1145000</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>CC103</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Water Treatment</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>488000</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>488000</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>CC104</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Preform Production</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>198000</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>198000</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CC105</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Filling &amp; Packaging</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>645000</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>645000</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>CC201</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Factory Utilities</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>CC202</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>140000</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>CC301</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>565000</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>565000</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>CC302</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>1230500</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1230500</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n">
+        <v>7671500</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>7671500</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>